--- a/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/claude-haiku-4-5/heterogeneity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/claude-haiku-4-5/heterogeneity.xlsx
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>3.452205882352941</v>
+        <v>3.506066176470588</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2781982034963909</v>
+        <v>0.4012773565186051</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04917895905155326</v>
+        <v>0.07093648498272936</v>
       </c>
       <c r="J8" t="n">
         <v>2.510294117647059</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9419117647058823</v>
+        <v>0.9957720588235297</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>1.890992647058823</v>
+        <v>2.119301470588235</v>
       </c>
       <c r="H9" t="n">
-        <v>0.450096997830678</v>
+        <v>0.3624716850429336</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07956665983944479</v>
+        <v>0.06407654662049321</v>
       </c>
       <c r="J9" t="n">
         <v>1.306066176470588</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5849264705882349</v>
+        <v>0.8132352941176468</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>3.049816176470588</v>
+        <v>3.084558823529412</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4440802210376196</v>
+        <v>0.3876245843530957</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07850303392163044</v>
+        <v>0.06852299303767272</v>
       </c>
       <c r="J10" t="n">
         <v>1.687132352941176</v>
       </c>
       <c r="K10" t="n">
-        <v>1.362683823529412</v>
+        <v>1.397426470588235</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>3.452205882352941</v>
+        <v>3.506066176470588</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2781982034963909</v>
+        <v>0.4012773565186051</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04917895905155326</v>
+        <v>0.07093648498272936</v>
       </c>
       <c r="J11" t="n">
         <v>2.510294117647059</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9419117647058823</v>
+        <v>0.9957720588235297</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -932,19 +932,19 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>1.890992647058823</v>
+        <v>2.119301470588235</v>
       </c>
       <c r="H12" t="n">
-        <v>0.450096997830678</v>
+        <v>0.3624716850429336</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07956665983944479</v>
+        <v>0.06407654662049321</v>
       </c>
       <c r="J12" t="n">
         <v>1.306066176470588</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5849264705882349</v>
+        <v>0.8132352941176468</v>
       </c>
     </row>
     <row r="13">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>3.049816176470588</v>
+        <v>3.084558823529412</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4440802210376196</v>
+        <v>0.3876245843530957</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07850303392163044</v>
+        <v>0.06852299303767272</v>
       </c>
       <c r="J13" t="n">
         <v>1.687132352941176</v>
       </c>
       <c r="K13" t="n">
-        <v>1.362683823529412</v>
+        <v>1.397426470588235</v>
       </c>
     </row>
     <row r="14">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1792,19 +1792,19 @@
         <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>3.90625</v>
+        <v>3.986979166666667</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1566191874978067</v>
+        <v>0.06027630153619019</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02768662238590662</v>
+        <v>0.0106554453902713</v>
       </c>
       <c r="J32" t="n">
         <v>3.5234375</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3828125</v>
+        <v>0.4635416666666665</v>
       </c>
     </row>
     <row r="33">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1835,19 +1835,19 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>1.653645833333333</v>
+        <v>1.838541666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.458447871807553</v>
+        <v>0.3959571113772036</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08104289974391543</v>
+        <v>0.06999598962846443</v>
       </c>
       <c r="J33" t="n">
         <v>1.177083333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4765625000000002</v>
+        <v>0.6614583333333333</v>
       </c>
     </row>
     <row r="34">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1878,19 +1878,19 @@
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>2.869791666666667</v>
+        <v>3.0546875</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4632253587347204</v>
+        <v>0.4806326918741669</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08188744809472298</v>
+        <v>0.08496465892104196</v>
       </c>
       <c r="J34" t="n">
         <v>1.794270833333333</v>
       </c>
       <c r="K34" t="n">
-        <v>1.075520833333333</v>
+        <v>1.260416666666667</v>
       </c>
     </row>
     <row r="35">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1921,19 +1921,19 @@
         <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>3.90625</v>
+        <v>3.986979166666667</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1566191874978067</v>
+        <v>0.06027630153619019</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02768662238590662</v>
+        <v>0.0106554453902713</v>
       </c>
       <c r="J35" t="n">
         <v>3.5234375</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3828125</v>
+        <v>0.4635416666666665</v>
       </c>
     </row>
     <row r="36">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1964,19 +1964,19 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>1.653645833333333</v>
+        <v>1.838541666666667</v>
       </c>
       <c r="H36" t="n">
-        <v>0.458447871807553</v>
+        <v>0.3959571113772036</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08104289974391543</v>
+        <v>0.06999598962846443</v>
       </c>
       <c r="J36" t="n">
         <v>1.177083333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4765625000000002</v>
+        <v>0.6614583333333333</v>
       </c>
     </row>
     <row r="37">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>2.869791666666667</v>
+        <v>3.0546875</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4632253587347204</v>
+        <v>0.4806326918741669</v>
       </c>
       <c r="I37" t="n">
-        <v>0.08188744809472298</v>
+        <v>0.08496465892104196</v>
       </c>
       <c r="J37" t="n">
         <v>1.794270833333333</v>
       </c>
       <c r="K37" t="n">
-        <v>1.075520833333333</v>
+        <v>1.260416666666667</v>
       </c>
     </row>
     <row r="38">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2824,19 +2824,19 @@
         <v>32</v>
       </c>
       <c r="G56" t="n">
-        <v>3.671875</v>
+        <v>3.77734375</v>
       </c>
       <c r="H56" t="n">
-        <v>0.400037800633245</v>
+        <v>0.3806488187102173</v>
       </c>
       <c r="I56" t="n">
-        <v>0.07071736038967992</v>
+        <v>0.06728984024016085</v>
       </c>
       <c r="J56" t="n">
         <v>3.2421875</v>
       </c>
       <c r="K56" t="n">
-        <v>0.4296875</v>
+        <v>0.53515625</v>
       </c>
     </row>
     <row r="57">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
         <v>32</v>
       </c>
       <c r="G57" t="n">
-        <v>1.62109375</v>
+        <v>1.94921875</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5439220389686434</v>
+        <v>0.5543626235116994</v>
       </c>
       <c r="I57" t="n">
-        <v>0.09615274054788532</v>
+        <v>0.09799839258037191</v>
       </c>
       <c r="J57" t="n">
         <v>1.140625</v>
       </c>
       <c r="K57" t="n">
-        <v>0.48046875</v>
+        <v>0.80859375</v>
       </c>
     </row>
     <row r="58">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2910,19 +2910,19 @@
         <v>32</v>
       </c>
       <c r="G58" t="n">
-        <v>2.9140625</v>
+        <v>2.8984375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2739302875173807</v>
+        <v>0.3019384617391752</v>
       </c>
       <c r="I58" t="n">
-        <v>0.04842449096898013</v>
+        <v>0.05337568344920143</v>
       </c>
       <c r="J58" t="n">
         <v>1.890625</v>
       </c>
       <c r="K58" t="n">
-        <v>1.0234375</v>
+        <v>1.0078125</v>
       </c>
     </row>
     <row r="59">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2953,19 +2953,19 @@
         <v>32</v>
       </c>
       <c r="G59" t="n">
-        <v>3.671875</v>
+        <v>3.77734375</v>
       </c>
       <c r="H59" t="n">
-        <v>0.400037800633245</v>
+        <v>0.3806488187102173</v>
       </c>
       <c r="I59" t="n">
-        <v>0.07071736038967992</v>
+        <v>0.06728984024016085</v>
       </c>
       <c r="J59" t="n">
         <v>3.2421875</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4296875</v>
+        <v>0.53515625</v>
       </c>
     </row>
     <row r="60">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         <v>32</v>
       </c>
       <c r="G60" t="n">
-        <v>1.62109375</v>
+        <v>1.94921875</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5439220389686434</v>
+        <v>0.5543626235116994</v>
       </c>
       <c r="I60" t="n">
-        <v>0.09615274054788532</v>
+        <v>0.09799839258037191</v>
       </c>
       <c r="J60" t="n">
         <v>1.140625</v>
       </c>
       <c r="K60" t="n">
-        <v>0.48046875</v>
+        <v>0.80859375</v>
       </c>
     </row>
     <row r="61">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3039,19 +3039,19 @@
         <v>32</v>
       </c>
       <c r="G61" t="n">
-        <v>2.9140625</v>
+        <v>2.8984375</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2739302875173807</v>
+        <v>0.3019384617391752</v>
       </c>
       <c r="I61" t="n">
-        <v>0.04842449096898013</v>
+        <v>0.05337568344920143</v>
       </c>
       <c r="J61" t="n">
         <v>1.890625</v>
       </c>
       <c r="K61" t="n">
-        <v>1.0234375</v>
+        <v>1.0078125</v>
       </c>
     </row>
     <row r="62">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3859,10 +3859,10 @@
         <v>4.010416666666667</v>
       </c>
       <c r="H80" t="n">
-        <v>0.05892556509887902</v>
+        <v>0.07255575041003112</v>
       </c>
       <c r="I80" t="n">
-        <v>0.01041666666666668</v>
+        <v>0.01282616578225291</v>
       </c>
       <c r="J80" t="n">
         <v>3.734375</v>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3899,19 +3899,19 @@
         <v>32</v>
       </c>
       <c r="G81" t="n">
-        <v>1.953125</v>
+        <v>2.234375</v>
       </c>
       <c r="H81" t="n">
-        <v>0.6167238784852641</v>
+        <v>0.5939651326913445</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1090224091491496</v>
+        <v>0.1049991932786043</v>
       </c>
       <c r="J81" t="n">
         <v>1.354166666666667</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5989583333333333</v>
+        <v>0.8802083333333333</v>
       </c>
     </row>
     <row r="82">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3942,19 +3942,19 @@
         <v>32</v>
       </c>
       <c r="G82" t="n">
-        <v>3.328125</v>
+        <v>3.453125</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3209650965291463</v>
+        <v>0.4301253776537629</v>
       </c>
       <c r="I82" t="n">
-        <v>0.05673914906998853</v>
+        <v>0.07603614282485011</v>
       </c>
       <c r="J82" t="n">
         <v>2.229166666666667</v>
       </c>
       <c r="K82" t="n">
-        <v>1.098958333333333</v>
+        <v>1.223958333333333</v>
       </c>
     </row>
     <row r="83">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
         <v>4.010416666666667</v>
       </c>
       <c r="H83" t="n">
-        <v>0.05892556509887902</v>
+        <v>0.07255575041003112</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01041666666666668</v>
+        <v>0.01282616578225291</v>
       </c>
       <c r="J83" t="n">
         <v>3.734375</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4028,19 +4028,19 @@
         <v>32</v>
       </c>
       <c r="G84" t="n">
-        <v>1.953125</v>
+        <v>2.234375</v>
       </c>
       <c r="H84" t="n">
-        <v>0.6167238784852641</v>
+        <v>0.5939651326913445</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1090224091491496</v>
+        <v>0.1049991932786043</v>
       </c>
       <c r="J84" t="n">
         <v>1.354166666666667</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5989583333333333</v>
+        <v>0.8802083333333333</v>
       </c>
     </row>
     <row r="85">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4071,19 +4071,19 @@
         <v>32</v>
       </c>
       <c r="G85" t="n">
-        <v>3.328125</v>
+        <v>3.453125</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3209650965291463</v>
+        <v>0.4301253776537629</v>
       </c>
       <c r="I85" t="n">
-        <v>0.05673914906998853</v>
+        <v>0.07603614282485011</v>
       </c>
       <c r="J85" t="n">
         <v>2.229166666666667</v>
       </c>
       <c r="K85" t="n">
-        <v>1.098958333333333</v>
+        <v>1.223958333333333</v>
       </c>
     </row>
     <row r="86">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4888,19 +4888,19 @@
         <v>32</v>
       </c>
       <c r="G104" t="n">
-        <v>2.53125</v>
+        <v>2.734375</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2892565553945315</v>
+        <v>0.453203205153373</v>
       </c>
       <c r="I104" t="n">
-        <v>0.05113381795553386</v>
+        <v>0.08011576490485703</v>
       </c>
       <c r="J104" t="n">
         <v>2.46875</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0625</v>
+        <v>0.265625</v>
       </c>
     </row>
     <row r="105">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4931,19 +4931,19 @@
         <v>32</v>
       </c>
       <c r="G105" t="n">
-        <v>1.828125</v>
+        <v>1.9609375</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3936875910602704</v>
+        <v>0.2847563687016131</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0695947913269284</v>
+        <v>0.05033828982374185</v>
       </c>
       <c r="J105" t="n">
         <v>1.3125</v>
       </c>
       <c r="K105" t="n">
-        <v>0.515625</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="106">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
         <v>32</v>
       </c>
       <c r="G106" t="n">
-        <v>2.1953125</v>
+        <v>2.3359375</v>
       </c>
       <c r="H106" t="n">
-        <v>0.2175224775185462</v>
+        <v>0.3735691789369312</v>
       </c>
       <c r="I106" t="n">
-        <v>0.03845290472846559</v>
+        <v>0.0660383249171487</v>
       </c>
       <c r="J106" t="n">
         <v>1.7109375</v>
       </c>
       <c r="K106" t="n">
-        <v>0.484375</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="107">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5017,19 +5017,19 @@
         <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>2.53125</v>
+        <v>2.734375</v>
       </c>
       <c r="H107" t="n">
-        <v>0.2892565553945315</v>
+        <v>0.453203205153373</v>
       </c>
       <c r="I107" t="n">
-        <v>0.05113381795553386</v>
+        <v>0.08011576490485703</v>
       </c>
       <c r="J107" t="n">
         <v>2.46875</v>
       </c>
       <c r="K107" t="n">
-        <v>0.0625</v>
+        <v>0.265625</v>
       </c>
     </row>
     <row r="108">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5060,19 +5060,19 @@
         <v>32</v>
       </c>
       <c r="G108" t="n">
-        <v>1.828125</v>
+        <v>1.9609375</v>
       </c>
       <c r="H108" t="n">
-        <v>0.3936875910602704</v>
+        <v>0.2847563687016131</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0695947913269284</v>
+        <v>0.05033828982374185</v>
       </c>
       <c r="J108" t="n">
         <v>1.3125</v>
       </c>
       <c r="K108" t="n">
-        <v>0.515625</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="109">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5103,19 +5103,19 @@
         <v>32</v>
       </c>
       <c r="G109" t="n">
-        <v>2.1953125</v>
+        <v>2.3359375</v>
       </c>
       <c r="H109" t="n">
-        <v>0.2175224775185462</v>
+        <v>0.3735691789369312</v>
       </c>
       <c r="I109" t="n">
-        <v>0.03845290472846559</v>
+        <v>0.0660383249171487</v>
       </c>
       <c r="J109" t="n">
         <v>1.7109375</v>
       </c>
       <c r="K109" t="n">
-        <v>0.484375</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="110">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5920,19 +5920,19 @@
         <v>32</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9553199404761905</v>
+        <v>0.9745926816239316</v>
       </c>
       <c r="H128" t="n">
-        <v>0.06428214729180622</v>
+        <v>0.05054638321251809</v>
       </c>
       <c r="I128" t="n">
-        <v>0.01136358556481716</v>
+        <v>0.008935422583506351</v>
       </c>
       <c r="J128" t="n">
         <v>0.9450247975064152</v>
       </c>
       <c r="K128" t="n">
-        <v>0.01029514296977529</v>
+        <v>0.02956788411751643</v>
       </c>
     </row>
     <row r="129">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5963,19 +5963,19 @@
         <v>32</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2496706692430377</v>
+        <v>0.3226982303740721</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2256869848598605</v>
+        <v>0.2318724924584012</v>
       </c>
       <c r="I129" t="n">
-        <v>0.03989619935498825</v>
+        <v>0.04098965294699052</v>
       </c>
       <c r="J129" t="n">
         <v>0.1474739774829163</v>
       </c>
       <c r="K129" t="n">
-        <v>0.1021966917601214</v>
+        <v>0.1752242528911558</v>
       </c>
     </row>
     <row r="130">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6006,19 +6006,19 @@
         <v>32</v>
       </c>
       <c r="G130" t="n">
-        <v>0.661944218975469</v>
+        <v>0.7352005724538619</v>
       </c>
       <c r="H130" t="n">
-        <v>0.09627961147072311</v>
+        <v>0.101848478778466</v>
       </c>
       <c r="I130" t="n">
-        <v>0.01701999154023861</v>
+        <v>0.01800443749944687</v>
       </c>
       <c r="J130" t="n">
         <v>0.4271739153255529</v>
       </c>
       <c r="K130" t="n">
-        <v>0.2347703036499161</v>
+        <v>0.3080266571283091</v>
       </c>
     </row>
     <row r="131">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6049,19 +6049,19 @@
         <v>32</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9553199404761905</v>
+        <v>0.9745926816239316</v>
       </c>
       <c r="H131" t="n">
-        <v>0.06428214729180622</v>
+        <v>0.05054638321251809</v>
       </c>
       <c r="I131" t="n">
-        <v>0.01136358556481716</v>
+        <v>0.008935422583506351</v>
       </c>
       <c r="J131" t="n">
         <v>0.9450247975064152</v>
       </c>
       <c r="K131" t="n">
-        <v>0.01029514296977529</v>
+        <v>0.02956788411751643</v>
       </c>
     </row>
     <row r="132">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6092,19 +6092,19 @@
         <v>32</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2496706692430377</v>
+        <v>0.3226982303740721</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2256869848598605</v>
+        <v>0.2318724924584012</v>
       </c>
       <c r="I132" t="n">
-        <v>0.03989619935498825</v>
+        <v>0.04098965294699052</v>
       </c>
       <c r="J132" t="n">
         <v>0.1474739774829163</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1021966917601214</v>
+        <v>0.1752242528911558</v>
       </c>
     </row>
     <row r="133">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6135,19 +6135,19 @@
         <v>32</v>
       </c>
       <c r="G133" t="n">
-        <v>0.661944218975469</v>
+        <v>0.7352005724538619</v>
       </c>
       <c r="H133" t="n">
-        <v>0.09627961147072311</v>
+        <v>0.101848478778466</v>
       </c>
       <c r="I133" t="n">
-        <v>0.01701999154023861</v>
+        <v>0.01800443749944687</v>
       </c>
       <c r="J133" t="n">
         <v>0.4271739153255529</v>
       </c>
       <c r="K133" t="n">
-        <v>0.2347703036499161</v>
+        <v>0.3080266571283091</v>
       </c>
     </row>
     <row r="134">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -6952,19 +6952,19 @@
         <v>32</v>
       </c>
       <c r="G152" t="n">
-        <v>0.5188835903679654</v>
+        <v>0.4208680555555556</v>
       </c>
       <c r="H152" t="n">
-        <v>0.2117337531779495</v>
+        <v>0.1684333577261302</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0374295931695517</v>
+        <v>0.02977509235654156</v>
       </c>
       <c r="J152" t="n">
         <v>0.2979604076479077</v>
       </c>
       <c r="K152" t="n">
-        <v>0.2209231827200577</v>
+        <v>0.1229076479076479</v>
       </c>
     </row>
     <row r="153">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -6995,19 +6995,19 @@
         <v>32</v>
       </c>
       <c r="G153" t="n">
-        <v>0.7114780084844823</v>
+        <v>0.6464295017632866</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2784430310465995</v>
+        <v>0.2451604062535511</v>
       </c>
       <c r="I153" t="n">
-        <v>0.04922223885679671</v>
+        <v>0.04333864643508371</v>
       </c>
       <c r="J153" t="n">
         <v>0.4127582463331302</v>
       </c>
       <c r="K153" t="n">
-        <v>0.298719762151352</v>
+        <v>0.2336712554301564</v>
       </c>
     </row>
     <row r="154">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7038,19 +7038,19 @@
         <v>32</v>
       </c>
       <c r="G154" t="n">
-        <v>0.7096088807026306</v>
+        <v>0.6581695822134895</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2235600378221453</v>
+        <v>0.2345852468674586</v>
       </c>
       <c r="I154" t="n">
-        <v>0.03952020468658999</v>
+        <v>0.04146920470657506</v>
       </c>
       <c r="J154" t="n">
         <v>0.2685587671111568</v>
       </c>
       <c r="K154" t="n">
-        <v>0.4410501135914738</v>
+        <v>0.3896108151023327</v>
       </c>
     </row>
     <row r="155">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7081,19 +7081,19 @@
         <v>32</v>
       </c>
       <c r="G155" t="n">
-        <v>0.5188835903679654</v>
+        <v>0.4208680555555556</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2117337531779495</v>
+        <v>0.1684333577261302</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0374295931695517</v>
+        <v>0.02977509235654156</v>
       </c>
       <c r="J155" t="n">
         <v>0.2979604076479077</v>
       </c>
       <c r="K155" t="n">
-        <v>0.2209231827200577</v>
+        <v>0.1229076479076479</v>
       </c>
     </row>
     <row r="156">
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7124,19 +7124,19 @@
         <v>32</v>
       </c>
       <c r="G156" t="n">
-        <v>0.7114780084844823</v>
+        <v>0.6464295017632866</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2784430310465995</v>
+        <v>0.2451604062535511</v>
       </c>
       <c r="I156" t="n">
-        <v>0.04922223885679671</v>
+        <v>0.04333864643508371</v>
       </c>
       <c r="J156" t="n">
         <v>0.4127582463331302</v>
       </c>
       <c r="K156" t="n">
-        <v>0.298719762151352</v>
+        <v>0.2336712554301564</v>
       </c>
     </row>
     <row r="157">
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7167,19 +7167,19 @@
         <v>32</v>
       </c>
       <c r="G157" t="n">
-        <v>0.7096088807026306</v>
+        <v>0.6581695822134895</v>
       </c>
       <c r="H157" t="n">
-        <v>0.2235600378221453</v>
+        <v>0.2345852468674586</v>
       </c>
       <c r="I157" t="n">
-        <v>0.03952020468658999</v>
+        <v>0.04146920470657506</v>
       </c>
       <c r="J157" t="n">
         <v>0.2685587671111568</v>
       </c>
       <c r="K157" t="n">
-        <v>0.4410501135914738</v>
+        <v>0.3896108151023327</v>
       </c>
     </row>
     <row r="158">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -7984,19 +7984,19 @@
         <v>32</v>
       </c>
       <c r="G176" t="n">
-        <v>3.65625</v>
+        <v>3.65</v>
       </c>
       <c r="H176" t="n">
-        <v>0.3600515196110045</v>
+        <v>0.4428645755285294</v>
       </c>
       <c r="I176" t="n">
-        <v>0.06364871777336562</v>
+        <v>0.07828813612588127</v>
       </c>
       <c r="J176" t="n">
         <v>2.39375</v>
       </c>
       <c r="K176" t="n">
-        <v>1.2625</v>
+        <v>1.256250000000001</v>
       </c>
     </row>
     <row r="177">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8027,19 +8027,19 @@
         <v>32</v>
       </c>
       <c r="G177" t="n">
-        <v>1.63125</v>
+        <v>1.8875</v>
       </c>
       <c r="H177" t="n">
-        <v>0.6265303844033784</v>
+        <v>0.4870914334251107</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1107559708577608</v>
+        <v>0.08610641390819289</v>
       </c>
       <c r="J177" t="n">
         <v>1.0625</v>
       </c>
       <c r="K177" t="n">
-        <v>0.5687500000000001</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="178">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8070,19 +8070,19 @@
         <v>32</v>
       </c>
       <c r="G178" t="n">
-        <v>3.14375</v>
+        <v>3.15625</v>
       </c>
       <c r="H178" t="n">
-        <v>0.5085954726879798</v>
+        <v>0.4703721930556695</v>
       </c>
       <c r="I178" t="n">
-        <v>0.08990782690461201</v>
+        <v>0.08315084184781293</v>
       </c>
       <c r="J178" t="n">
         <v>1.5875</v>
       </c>
       <c r="K178" t="n">
-        <v>1.55625</v>
+        <v>1.56875</v>
       </c>
     </row>
     <row r="179">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8113,19 +8113,19 @@
         <v>32</v>
       </c>
       <c r="G179" t="n">
-        <v>3.65625</v>
+        <v>3.65</v>
       </c>
       <c r="H179" t="n">
-        <v>0.3600515196110045</v>
+        <v>0.4428645755285294</v>
       </c>
       <c r="I179" t="n">
-        <v>0.06364871777336562</v>
+        <v>0.07828813612588127</v>
       </c>
       <c r="J179" t="n">
         <v>2.39375</v>
       </c>
       <c r="K179" t="n">
-        <v>1.2625</v>
+        <v>1.256250000000001</v>
       </c>
     </row>
     <row r="180">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8156,19 +8156,19 @@
         <v>32</v>
       </c>
       <c r="G180" t="n">
-        <v>1.63125</v>
+        <v>1.8875</v>
       </c>
       <c r="H180" t="n">
-        <v>0.6265303844033784</v>
+        <v>0.4870914334251107</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1107559708577608</v>
+        <v>0.08610641390819289</v>
       </c>
       <c r="J180" t="n">
         <v>1.0625</v>
       </c>
       <c r="K180" t="n">
-        <v>0.5687500000000001</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="181">
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8199,19 +8199,19 @@
         <v>32</v>
       </c>
       <c r="G181" t="n">
-        <v>3.14375</v>
+        <v>3.15625</v>
       </c>
       <c r="H181" t="n">
-        <v>0.5085954726879798</v>
+        <v>0.4703721930556695</v>
       </c>
       <c r="I181" t="n">
-        <v>0.08990782690461201</v>
+        <v>0.08315084184781293</v>
       </c>
       <c r="J181" t="n">
         <v>1.5875</v>
       </c>
       <c r="K181" t="n">
-        <v>1.55625</v>
+        <v>1.56875</v>
       </c>
     </row>
     <row r="182">
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -9016,19 +9016,19 @@
         <v>32</v>
       </c>
       <c r="G200" t="n">
-        <v>3.248161764705882</v>
+        <v>3.362132352941177</v>
       </c>
       <c r="H200" t="n">
-        <v>0.3068348820235919</v>
+        <v>0.4480139041481629</v>
       </c>
       <c r="I200" t="n">
-        <v>0.05424125644586403</v>
+        <v>0.07919841742225647</v>
       </c>
       <c r="J200" t="n">
         <v>2.626838235294118</v>
       </c>
       <c r="K200" t="n">
-        <v>0.6213235294117645</v>
+        <v>0.7352941176470589</v>
       </c>
     </row>
     <row r="201">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9059,19 +9059,19 @@
         <v>32</v>
       </c>
       <c r="G201" t="n">
-        <v>2.150735294117647</v>
+        <v>2.351102941176471</v>
       </c>
       <c r="H201" t="n">
-        <v>0.3377295947361152</v>
+        <v>0.2933517066548256</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0597027216613229</v>
+        <v>0.0518577452620685</v>
       </c>
       <c r="J201" t="n">
         <v>1.549632352941176</v>
       </c>
       <c r="K201" t="n">
-        <v>0.6011029411764703</v>
+        <v>0.8014705882352942</v>
       </c>
     </row>
     <row r="202">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -9102,19 +9102,19 @@
         <v>32</v>
       </c>
       <c r="G202" t="n">
-        <v>2.955882352941177</v>
+        <v>3.012867647058823</v>
       </c>
       <c r="H202" t="n">
-        <v>0.4384164138030786</v>
+        <v>0.3855100644892749</v>
       </c>
       <c r="I202" t="n">
-        <v>0.07750180479591108</v>
+        <v>0.06814919520400738</v>
       </c>
       <c r="J202" t="n">
         <v>1.786764705882353</v>
       </c>
       <c r="K202" t="n">
-        <v>1.169117647058824</v>
+        <v>1.22610294117647</v>
       </c>
     </row>
     <row r="203">
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -9145,19 +9145,19 @@
         <v>32</v>
       </c>
       <c r="G203" t="n">
-        <v>3.248161764705882</v>
+        <v>3.362132352941177</v>
       </c>
       <c r="H203" t="n">
-        <v>0.3068348820235919</v>
+        <v>0.4480139041481629</v>
       </c>
       <c r="I203" t="n">
-        <v>0.05424125644586403</v>
+        <v>0.07919841742225647</v>
       </c>
       <c r="J203" t="n">
         <v>2.626838235294118</v>
       </c>
       <c r="K203" t="n">
-        <v>0.6213235294117645</v>
+        <v>0.7352941176470589</v>
       </c>
     </row>
     <row r="204">
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -9188,19 +9188,19 @@
         <v>32</v>
       </c>
       <c r="G204" t="n">
-        <v>2.150735294117647</v>
+        <v>2.351102941176471</v>
       </c>
       <c r="H204" t="n">
-        <v>0.3377295947361152</v>
+        <v>0.2933517066548256</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0597027216613229</v>
+        <v>0.0518577452620685</v>
       </c>
       <c r="J204" t="n">
         <v>1.549632352941176</v>
       </c>
       <c r="K204" t="n">
-        <v>0.6011029411764703</v>
+        <v>0.8014705882352942</v>
       </c>
     </row>
     <row r="205">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -9231,19 +9231,19 @@
         <v>32</v>
       </c>
       <c r="G205" t="n">
-        <v>2.955882352941177</v>
+        <v>3.012867647058823</v>
       </c>
       <c r="H205" t="n">
-        <v>0.4384164138030786</v>
+        <v>0.3855100644892749</v>
       </c>
       <c r="I205" t="n">
-        <v>0.07750180479591108</v>
+        <v>0.06814919520400738</v>
       </c>
       <c r="J205" t="n">
         <v>1.786764705882353</v>
       </c>
       <c r="K205" t="n">
-        <v>1.169117647058824</v>
+        <v>1.22610294117647</v>
       </c>
     </row>
     <row r="206">
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -10033,19 +10033,19 @@
         <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.764093137254902</v>
+        <v>2.956495098039216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7452697424462268</v>
+        <v>0.6802076019688694</v>
       </c>
       <c r="I6" t="n">
-        <v>0.107570421605053</v>
+        <v>0.09817951052538915</v>
       </c>
       <c r="J6" t="n">
         <v>1.857107843137255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9069852941176471</v>
+        <v>1.099387254901961</v>
       </c>
     </row>
     <row r="7">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -10076,19 +10076,19 @@
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.83125</v>
+        <v>2.850122549019608</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8072730901510432</v>
+        <v>0.7153577527348811</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1165198339770615</v>
+        <v>0.1032529977770923</v>
       </c>
       <c r="J7" t="n">
         <v>1.811887254901961</v>
       </c>
       <c r="K7" t="n">
-        <v>1.01936274509804</v>
+        <v>1.038235294117647</v>
       </c>
     </row>
     <row r="8">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10119,19 +10119,19 @@
         <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.764093137254902</v>
+        <v>2.956495098039216</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7452697424462268</v>
+        <v>0.6802076019688694</v>
       </c>
       <c r="I8" t="n">
-        <v>0.107570421605053</v>
+        <v>0.09817951052538915</v>
       </c>
       <c r="J8" t="n">
         <v>1.857107843137255</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9069852941176471</v>
+        <v>1.099387254901961</v>
       </c>
     </row>
     <row r="9">
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10162,19 +10162,19 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>2.83125</v>
+        <v>2.850122549019608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8072730901510432</v>
+        <v>0.7153577527348811</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1165198339770615</v>
+        <v>0.1032529977770923</v>
       </c>
       <c r="J9" t="n">
         <v>1.811887254901961</v>
       </c>
       <c r="K9" t="n">
-        <v>1.01936274509804</v>
+        <v>1.038235294117647</v>
       </c>
     </row>
     <row r="10">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -10721,19 +10721,19 @@
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>2.796875</v>
+        <v>3.024305555555556</v>
       </c>
       <c r="H22" t="n">
-        <v>1.004261935976869</v>
+        <v>0.9125404122229932</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1449527247682851</v>
+        <v>0.1317138631608393</v>
       </c>
       <c r="J22" t="n">
         <v>2.288194444444444</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5086805555555558</v>
+        <v>0.7361111111111116</v>
       </c>
     </row>
     <row r="23">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -10764,19 +10764,19 @@
         <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.822916666666667</v>
+        <v>2.895833333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>1.009210684482561</v>
+        <v>0.9987433001873058</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1456670150887633</v>
+        <v>0.1441561783036191</v>
       </c>
       <c r="J23" t="n">
         <v>2.041666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>0.78125</v>
+        <v>0.854166666666667</v>
       </c>
     </row>
     <row r="24">
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -10807,19 +10807,19 @@
         <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>2.796875</v>
+        <v>3.024305555555556</v>
       </c>
       <c r="H24" t="n">
-        <v>1.004261935976869</v>
+        <v>0.9125404122229932</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1449527247682851</v>
+        <v>0.1317138631608393</v>
       </c>
       <c r="J24" t="n">
         <v>2.288194444444444</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5086805555555558</v>
+        <v>0.7361111111111116</v>
       </c>
     </row>
     <row r="25">
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -10850,19 +10850,19 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>2.822916666666667</v>
+        <v>2.895833333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>1.009210684482561</v>
+        <v>0.9987433001873058</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1456670150887633</v>
+        <v>0.1441561783036191</v>
       </c>
       <c r="J25" t="n">
         <v>2.041666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.78125</v>
+        <v>0.854166666666667</v>
       </c>
     </row>
     <row r="26">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -11409,19 +11409,19 @@
         <v>48</v>
       </c>
       <c r="G38" t="n">
-        <v>2.807291666666667</v>
+        <v>2.966145833333333</v>
       </c>
       <c r="H38" t="n">
-        <v>1.013525004327551</v>
+        <v>0.8386204728177568</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1462897335197321</v>
+        <v>0.1210444389323158</v>
       </c>
       <c r="J38" t="n">
         <v>2.197916666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>0.609375</v>
+        <v>0.768229166666667</v>
       </c>
     </row>
     <row r="39">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -11452,19 +11452,19 @@
         <v>48</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6640625</v>
+        <v>2.783854166666667</v>
       </c>
       <c r="H39" t="n">
-        <v>0.881305641822694</v>
+        <v>0.8811484524763228</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1272055123861671</v>
+        <v>0.1271828240583068</v>
       </c>
       <c r="J39" t="n">
         <v>1.984375</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6796875</v>
+        <v>0.7994791666666665</v>
       </c>
     </row>
     <row r="40">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -11495,19 +11495,19 @@
         <v>48</v>
       </c>
       <c r="G40" t="n">
-        <v>2.807291666666667</v>
+        <v>2.966145833333333</v>
       </c>
       <c r="H40" t="n">
-        <v>1.013525004327551</v>
+        <v>0.8386204728177568</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1462897335197321</v>
+        <v>0.1210444389323158</v>
       </c>
       <c r="J40" t="n">
         <v>2.197916666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>0.609375</v>
+        <v>0.768229166666667</v>
       </c>
     </row>
     <row r="41">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -11538,19 +11538,19 @@
         <v>48</v>
       </c>
       <c r="G41" t="n">
-        <v>2.6640625</v>
+        <v>2.783854166666667</v>
       </c>
       <c r="H41" t="n">
-        <v>0.881305641822694</v>
+        <v>0.8811484524763228</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1272055123861671</v>
+        <v>0.1271828240583068</v>
       </c>
       <c r="J41" t="n">
         <v>1.984375</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6796875</v>
+        <v>0.7994791666666665</v>
       </c>
     </row>
     <row r="42">
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -12097,19 +12097,19 @@
         <v>48</v>
       </c>
       <c r="G54" t="n">
-        <v>3.107638888888889</v>
+        <v>3.28125</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9666358416052074</v>
+        <v>0.8093398719751761</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1395218658397767</v>
+        <v>0.1168181482376913</v>
       </c>
       <c r="J54" t="n">
         <v>2.524305555555556</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5833333333333335</v>
+        <v>0.7569444444444442</v>
       </c>
     </row>
     <row r="55">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -12140,19 +12140,19 @@
         <v>48</v>
       </c>
       <c r="G55" t="n">
-        <v>3.086805555555556</v>
+        <v>3.184027777777777</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9390337467112505</v>
+        <v>0.9065297556029467</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1355378466104708</v>
+        <v>0.1308462996064417</v>
       </c>
       <c r="J55" t="n">
         <v>2.354166666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7326388888888893</v>
+        <v>0.8298611111111107</v>
       </c>
     </row>
     <row r="56">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -12183,19 +12183,19 @@
         <v>48</v>
       </c>
       <c r="G56" t="n">
-        <v>3.107638888888889</v>
+        <v>3.28125</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9666358416052074</v>
+        <v>0.8093398719751761</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1395218658397767</v>
+        <v>0.1168181482376913</v>
       </c>
       <c r="J56" t="n">
         <v>2.524305555555556</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5833333333333335</v>
+        <v>0.7569444444444442</v>
       </c>
     </row>
     <row r="57">
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -12226,19 +12226,19 @@
         <v>48</v>
       </c>
       <c r="G57" t="n">
-        <v>3.086805555555556</v>
+        <v>3.184027777777777</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9390337467112505</v>
+        <v>0.9065297556029467</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1355378466104708</v>
+        <v>0.1308462996064417</v>
       </c>
       <c r="J57" t="n">
         <v>2.354166666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7326388888888893</v>
+        <v>0.8298611111111107</v>
       </c>
     </row>
     <row r="58">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -12785,19 +12785,19 @@
         <v>48</v>
       </c>
       <c r="G70" t="n">
-        <v>2.109375</v>
+        <v>2.421875</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4154792477599199</v>
+        <v>0.4588267009333281</v>
       </c>
       <c r="I70" t="n">
-        <v>0.05996926388422325</v>
+        <v>0.06622592982381123</v>
       </c>
       <c r="J70" t="n">
         <v>1.765625</v>
       </c>
       <c r="K70" t="n">
-        <v>0.34375</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="71">
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -12828,19 +12828,19 @@
         <v>48</v>
       </c>
       <c r="G71" t="n">
-        <v>2.260416666666667</v>
+        <v>2.265625</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4156459127944061</v>
+        <v>0.5115845482420281</v>
       </c>
       <c r="I71" t="n">
-        <v>0.05999331990985452</v>
+        <v>0.07384086916019701</v>
       </c>
       <c r="J71" t="n">
         <v>1.895833333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3645833333333333</v>
+        <v>0.3697916666666667</v>
       </c>
     </row>
     <row r="72">
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -12871,19 +12871,19 @@
         <v>48</v>
       </c>
       <c r="G72" t="n">
-        <v>2.109375</v>
+        <v>2.421875</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4154792477599199</v>
+        <v>0.4588267009333281</v>
       </c>
       <c r="I72" t="n">
-        <v>0.05996926388422325</v>
+        <v>0.06622592982381123</v>
       </c>
       <c r="J72" t="n">
         <v>1.765625</v>
       </c>
       <c r="K72" t="n">
-        <v>0.34375</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="73">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -12914,19 +12914,19 @@
         <v>48</v>
       </c>
       <c r="G73" t="n">
-        <v>2.260416666666667</v>
+        <v>2.265625</v>
       </c>
       <c r="H73" t="n">
-        <v>0.4156459127944061</v>
+        <v>0.5115845482420281</v>
       </c>
       <c r="I73" t="n">
-        <v>0.05999331990985452</v>
+        <v>0.07384086916019701</v>
       </c>
       <c r="J73" t="n">
         <v>1.895833333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3645833333333333</v>
+        <v>0.3697916666666667</v>
       </c>
     </row>
     <row r="74">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -13473,19 +13473,19 @@
         <v>48</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6200807416267943</v>
+        <v>0.699088046009002</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3304892658563851</v>
+        <v>0.2949433747004748</v>
       </c>
       <c r="I86" t="n">
-        <v>0.04770201665161643</v>
+        <v>0.04257140919475395</v>
       </c>
       <c r="J86" t="n">
         <v>0.5110360802055091</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1090446614212852</v>
+        <v>0.1880519658034929</v>
       </c>
     </row>
     <row r="87">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -13516,19 +13516,19 @@
         <v>48</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6245424775030038</v>
+        <v>0.6559062769589085</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3229820403273664</v>
+        <v>0.3226687220820985</v>
       </c>
       <c r="I87" t="n">
-        <v>0.04661844198160489</v>
+        <v>0.04657321838829303</v>
       </c>
       <c r="J87" t="n">
         <v>0.5020790466710804</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1224634308319235</v>
+        <v>0.1538272302878281</v>
       </c>
     </row>
     <row r="88">
@@ -13548,7 +13548,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -13559,19 +13559,19 @@
         <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6200807416267943</v>
+        <v>0.699088046009002</v>
       </c>
       <c r="H88" t="n">
-        <v>0.3304892658563851</v>
+        <v>0.2949433747004748</v>
       </c>
       <c r="I88" t="n">
-        <v>0.04770201665161643</v>
+        <v>0.04257140919475395</v>
       </c>
       <c r="J88" t="n">
         <v>0.5110360802055091</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1090446614212852</v>
+        <v>0.1880519658034929</v>
       </c>
     </row>
     <row r="89">
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -13602,19 +13602,19 @@
         <v>48</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6245424775030038</v>
+        <v>0.6559062769589085</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3229820403273664</v>
+        <v>0.3226687220820985</v>
       </c>
       <c r="I89" t="n">
-        <v>0.04661844198160489</v>
+        <v>0.04657321838829303</v>
       </c>
       <c r="J89" t="n">
         <v>0.5020790466710804</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1224634308319235</v>
+        <v>0.1538272302878281</v>
       </c>
     </row>
     <row r="90">
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -14161,19 +14161,19 @@
         <v>48</v>
       </c>
       <c r="G102" t="n">
-        <v>0.6633835231353613</v>
+        <v>0.5633979047877075</v>
       </c>
       <c r="H102" t="n">
-        <v>0.2763116078437594</v>
+        <v>0.2629434033969018</v>
       </c>
       <c r="I102" t="n">
-        <v>0.03988214529220321</v>
+        <v>0.0379526111832094</v>
       </c>
       <c r="J102" t="n">
         <v>0.2788127898789663</v>
       </c>
       <c r="K102" t="n">
-        <v>0.384570733256395</v>
+        <v>0.2845851149087411</v>
       </c>
     </row>
     <row r="103">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -14204,19 +14204,19 @@
         <v>48</v>
       </c>
       <c r="G103" t="n">
-        <v>0.6299301299013575</v>
+        <v>0.5869135215671804</v>
       </c>
       <c r="H103" t="n">
-        <v>0.2311418689836212</v>
+        <v>0.2226832406825554</v>
       </c>
       <c r="I103" t="n">
-        <v>0.03336245506967173</v>
+        <v>0.03214155723802289</v>
       </c>
       <c r="J103" t="n">
         <v>0.3740388241824968</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2558913057188608</v>
+        <v>0.2128746973846836</v>
       </c>
     </row>
     <row r="104">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -14247,19 +14247,19 @@
         <v>48</v>
       </c>
       <c r="G104" t="n">
-        <v>0.6633835231353613</v>
+        <v>0.5633979047877075</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2763116078437594</v>
+        <v>0.2629434033969018</v>
       </c>
       <c r="I104" t="n">
-        <v>0.03988214529220321</v>
+        <v>0.0379526111832094</v>
       </c>
       <c r="J104" t="n">
         <v>0.2788127898789663</v>
       </c>
       <c r="K104" t="n">
-        <v>0.384570733256395</v>
+        <v>0.2845851149087411</v>
       </c>
     </row>
     <row r="105">
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -14290,19 +14290,19 @@
         <v>48</v>
       </c>
       <c r="G105" t="n">
-        <v>0.6299301299013575</v>
+        <v>0.5869135215671804</v>
       </c>
       <c r="H105" t="n">
-        <v>0.2311418689836212</v>
+        <v>0.2226832406825554</v>
       </c>
       <c r="I105" t="n">
-        <v>0.03336245506967173</v>
+        <v>0.03214155723802289</v>
       </c>
       <c r="J105" t="n">
         <v>0.3740388241824968</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2558913057188608</v>
+        <v>0.2128746973846836</v>
       </c>
     </row>
     <row r="106">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -14849,19 +14849,19 @@
         <v>48</v>
       </c>
       <c r="G118" t="n">
-        <v>2.791666666666667</v>
+        <v>2.979166666666667</v>
       </c>
       <c r="H118" t="n">
-        <v>0.9961272526871751</v>
+        <v>0.8212492646023672</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1437785843715157</v>
+        <v>0.1185371209974897</v>
       </c>
       <c r="J118" t="n">
         <v>1.7375</v>
       </c>
       <c r="K118" t="n">
-        <v>1.054166666666666</v>
+        <v>1.241666666666666</v>
       </c>
     </row>
     <row r="119">
@@ -14881,7 +14881,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -14892,19 +14892,19 @@
         <v>48</v>
       </c>
       <c r="G119" t="n">
-        <v>2.829166666666667</v>
+        <v>2.816666666666666</v>
       </c>
       <c r="H119" t="n">
-        <v>1.01561391837926</v>
+        <v>0.9324717401075976</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1465912422922491</v>
+        <v>0.1345907025407101</v>
       </c>
       <c r="J119" t="n">
         <v>1.625</v>
       </c>
       <c r="K119" t="n">
-        <v>1.204166666666667</v>
+        <v>1.191666666666666</v>
       </c>
     </row>
     <row r="120">
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -14935,19 +14935,19 @@
         <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>2.791666666666667</v>
+        <v>2.979166666666667</v>
       </c>
       <c r="H120" t="n">
-        <v>0.9961272526871751</v>
+        <v>0.8212492646023672</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1437785843715157</v>
+        <v>0.1185371209974897</v>
       </c>
       <c r="J120" t="n">
         <v>1.7375</v>
       </c>
       <c r="K120" t="n">
-        <v>1.054166666666666</v>
+        <v>1.241666666666666</v>
       </c>
     </row>
     <row r="121">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -14978,19 +14978,19 @@
         <v>48</v>
       </c>
       <c r="G121" t="n">
-        <v>2.829166666666667</v>
+        <v>2.816666666666666</v>
       </c>
       <c r="H121" t="n">
-        <v>1.01561391837926</v>
+        <v>0.9324717401075976</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1465912422922491</v>
+        <v>0.1345907025407101</v>
       </c>
       <c r="J121" t="n">
         <v>1.625</v>
       </c>
       <c r="K121" t="n">
-        <v>1.204166666666667</v>
+        <v>1.191666666666666</v>
       </c>
     </row>
     <row r="122">
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -15537,19 +15537,19 @@
         <v>48</v>
       </c>
       <c r="G134" t="n">
-        <v>2.736519607843138</v>
+        <v>2.933823529411764</v>
       </c>
       <c r="H134" t="n">
-        <v>0.5442895690688715</v>
+        <v>0.5886888114065495</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0785614323047546</v>
+        <v>0.08496991093362305</v>
       </c>
       <c r="J134" t="n">
         <v>1.97671568627451</v>
       </c>
       <c r="K134" t="n">
-        <v>0.7598039215686276</v>
+        <v>0.9571078431372546</v>
       </c>
     </row>
     <row r="135">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -15580,19 +15580,19 @@
         <v>48</v>
       </c>
       <c r="G135" t="n">
-        <v>2.833333333333333</v>
+        <v>2.88357843137255</v>
       </c>
       <c r="H135" t="n">
-        <v>0.6347484484229031</v>
+        <v>0.5462473402365473</v>
       </c>
       <c r="I135" t="n">
-        <v>0.09161804689116511</v>
+        <v>0.07884401223242192</v>
       </c>
       <c r="J135" t="n">
         <v>1.998774509803922</v>
       </c>
       <c r="K135" t="n">
-        <v>0.8345588235294119</v>
+        <v>0.8848039215686281</v>
       </c>
     </row>
     <row r="136">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -15623,19 +15623,19 @@
         <v>48</v>
       </c>
       <c r="G136" t="n">
-        <v>2.736519607843138</v>
+        <v>2.933823529411764</v>
       </c>
       <c r="H136" t="n">
-        <v>0.5442895690688715</v>
+        <v>0.5886888114065495</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0785614323047546</v>
+        <v>0.08496991093362305</v>
       </c>
       <c r="J136" t="n">
         <v>1.97671568627451</v>
       </c>
       <c r="K136" t="n">
-        <v>0.7598039215686276</v>
+        <v>0.9571078431372546</v>
       </c>
     </row>
     <row r="137">
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -15666,19 +15666,19 @@
         <v>48</v>
       </c>
       <c r="G137" t="n">
-        <v>2.833333333333333</v>
+        <v>2.88357843137255</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6347484484229031</v>
+        <v>0.5462473402365473</v>
       </c>
       <c r="I137" t="n">
-        <v>0.09161804689116511</v>
+        <v>0.07884401223242192</v>
       </c>
       <c r="J137" t="n">
         <v>1.998774509803922</v>
       </c>
       <c r="K137" t="n">
-        <v>0.8345588235294119</v>
+        <v>0.8848039215686281</v>
       </c>
     </row>
     <row r="138">

--- a/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/claude-haiku-4-5/heterogeneity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/claude-haiku-4-5/heterogeneity.xlsx
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>3.506066176470588</v>
+        <v>3.446323529411765</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4012773565186051</v>
+        <v>0.58104476148177</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07093648498272936</v>
+        <v>0.1027151727541699</v>
       </c>
       <c r="J8" t="n">
         <v>2.510294117647059</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9957720588235297</v>
+        <v>0.9360294117647059</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.119301470588235</v>
+        <v>2.161213235294118</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3624716850429336</v>
+        <v>0.3177203491771992</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06407654662049321</v>
+        <v>0.05616555335603882</v>
       </c>
       <c r="J9" t="n">
         <v>1.306066176470588</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8132352941176468</v>
+        <v>0.8551470588235293</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>3.084558823529412</v>
+        <v>3.01139705882353</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3876245843530957</v>
+        <v>0.519121880207004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06852299303767272</v>
+        <v>0.09176865043917078</v>
       </c>
       <c r="J10" t="n">
         <v>1.687132352941176</v>
       </c>
       <c r="K10" t="n">
-        <v>1.397426470588235</v>
+        <v>1.324264705882353</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>3.506066176470588</v>
+        <v>3.407720588235294</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4012773565186051</v>
+        <v>0.4402037030115779</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07093648498272936</v>
+        <v>0.07781775587572892</v>
       </c>
       <c r="J11" t="n">
         <v>2.510294117647059</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9957720588235297</v>
+        <v>0.8974264705882353</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -932,19 +932,19 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>2.119301470588235</v>
+        <v>1.975551470588235</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3624716850429336</v>
+        <v>0.3524636534780647</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06407654662049321</v>
+        <v>0.06230735987403124</v>
       </c>
       <c r="J12" t="n">
         <v>1.306066176470588</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8132352941176468</v>
+        <v>0.669485294117647</v>
       </c>
     </row>
     <row r="13">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>3.084558823529412</v>
+        <v>3.352757352941176</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3876245843530957</v>
+        <v>0.421379967309903</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06852299303767272</v>
+        <v>0.07449015808524953</v>
       </c>
       <c r="J13" t="n">
         <v>1.687132352941176</v>
       </c>
       <c r="K13" t="n">
-        <v>1.397426470588235</v>
+        <v>1.665625</v>
       </c>
     </row>
     <row r="14">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1792,19 +1792,19 @@
         <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>3.986979166666667</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06027630153619019</v>
+        <v>0.2366507642696104</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0106554453902713</v>
+        <v>0.04183434004700515</v>
       </c>
       <c r="J32" t="n">
         <v>3.5234375</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4635416666666665</v>
+        <v>0.3932291666666665</v>
       </c>
     </row>
     <row r="33">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1835,19 +1835,19 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>1.838541666666667</v>
+        <v>2.028645833333333</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3959571113772036</v>
+        <v>0.3877661965771195</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06999598962846443</v>
+        <v>0.06854802677864924</v>
       </c>
       <c r="J33" t="n">
         <v>1.177083333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6614583333333333</v>
+        <v>0.8515624999999998</v>
       </c>
     </row>
     <row r="34">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1878,19 +1878,19 @@
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>3.0546875</v>
+        <v>2.927083333333333</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4806326918741669</v>
+        <v>0.4141050288397791</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08496465892104196</v>
+        <v>0.07320411850401465</v>
       </c>
       <c r="J34" t="n">
         <v>1.794270833333333</v>
       </c>
       <c r="K34" t="n">
-        <v>1.260416666666667</v>
+        <v>1.1328125</v>
       </c>
     </row>
     <row r="35">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1921,19 +1921,19 @@
         <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>3.986979166666667</v>
+        <v>3.971354166666667</v>
       </c>
       <c r="H35" t="n">
-        <v>0.06027630153619019</v>
+        <v>0.1050033601612887</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0106554453902713</v>
+        <v>0.01856214700435515</v>
       </c>
       <c r="J35" t="n">
         <v>3.5234375</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4635416666666665</v>
+        <v>0.447916666666667</v>
       </c>
     </row>
     <row r="36">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1964,19 +1964,19 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>1.838541666666667</v>
+        <v>1.765625</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3959571113772036</v>
+        <v>0.3870886069180217</v>
       </c>
       <c r="I36" t="n">
-        <v>0.06999598962846443</v>
+        <v>0.06842824471794677</v>
       </c>
       <c r="J36" t="n">
         <v>1.177083333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6614583333333333</v>
+        <v>0.5885416666666667</v>
       </c>
     </row>
     <row r="37">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>3.0546875</v>
+        <v>2.927083333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4806326918741669</v>
+        <v>0.4523683198171525</v>
       </c>
       <c r="I37" t="n">
-        <v>0.08496465892104196</v>
+        <v>0.07996817663416834</v>
       </c>
       <c r="J37" t="n">
         <v>1.794270833333333</v>
       </c>
       <c r="K37" t="n">
-        <v>1.260416666666667</v>
+        <v>1.1328125</v>
       </c>
     </row>
     <row r="38">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2824,19 +2824,19 @@
         <v>32</v>
       </c>
       <c r="G56" t="n">
-        <v>3.77734375</v>
+        <v>3.90625</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3806488187102173</v>
+        <v>0.2961445810802991</v>
       </c>
       <c r="I56" t="n">
-        <v>0.06728984024016085</v>
+        <v>0.0523514603733822</v>
       </c>
       <c r="J56" t="n">
         <v>3.2421875</v>
       </c>
       <c r="K56" t="n">
-        <v>0.53515625</v>
+        <v>0.6640625</v>
       </c>
     </row>
     <row r="57">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
         <v>32</v>
       </c>
       <c r="G57" t="n">
-        <v>1.94921875</v>
+        <v>1.9921875</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5543626235116994</v>
+        <v>0.4052795480859775</v>
       </c>
       <c r="I57" t="n">
-        <v>0.09799839258037191</v>
+        <v>0.07164397918195355</v>
       </c>
       <c r="J57" t="n">
         <v>1.140625</v>
       </c>
       <c r="K57" t="n">
-        <v>0.80859375</v>
+        <v>0.8515625</v>
       </c>
     </row>
     <row r="58">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2910,19 +2910,19 @@
         <v>32</v>
       </c>
       <c r="G58" t="n">
-        <v>2.8984375</v>
+        <v>2.90625</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3019384617391752</v>
+        <v>0.2961445810802991</v>
       </c>
       <c r="I58" t="n">
-        <v>0.05337568344920143</v>
+        <v>0.0523514603733822</v>
       </c>
       <c r="J58" t="n">
         <v>1.890625</v>
       </c>
       <c r="K58" t="n">
-        <v>1.0078125</v>
+        <v>1.015625</v>
       </c>
     </row>
     <row r="59">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2953,19 +2953,19 @@
         <v>32</v>
       </c>
       <c r="G59" t="n">
-        <v>3.77734375</v>
+        <v>3.63671875</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3806488187102173</v>
+        <v>0.472381764307218</v>
       </c>
       <c r="I59" t="n">
-        <v>0.06728984024016085</v>
+        <v>0.0835060872126248</v>
       </c>
       <c r="J59" t="n">
         <v>3.2421875</v>
       </c>
       <c r="K59" t="n">
-        <v>0.53515625</v>
+        <v>0.39453125</v>
       </c>
     </row>
     <row r="60">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         <v>32</v>
       </c>
       <c r="G60" t="n">
-        <v>1.94921875</v>
+        <v>1.8203125</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5543626235116994</v>
+        <v>0.4545219706176958</v>
       </c>
       <c r="I60" t="n">
-        <v>0.09799839258037191</v>
+        <v>0.08034889190551135</v>
       </c>
       <c r="J60" t="n">
         <v>1.140625</v>
       </c>
       <c r="K60" t="n">
-        <v>0.80859375</v>
+        <v>0.6796875</v>
       </c>
     </row>
     <row r="61">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3039,19 +3039,19 @@
         <v>32</v>
       </c>
       <c r="G61" t="n">
-        <v>2.8984375</v>
+        <v>2.91796875</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3019384617391752</v>
+        <v>0.2610643826629004</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05337568344920143</v>
+        <v>0.04615009882680415</v>
       </c>
       <c r="J61" t="n">
         <v>1.890625</v>
       </c>
       <c r="K61" t="n">
-        <v>1.0078125</v>
+        <v>1.02734375</v>
       </c>
     </row>
     <row r="62">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3856,19 +3856,19 @@
         <v>32</v>
       </c>
       <c r="G80" t="n">
-        <v>4.010416666666667</v>
+        <v>4.057291666666667</v>
       </c>
       <c r="H80" t="n">
-        <v>0.07255575041003112</v>
+        <v>0.1672536705802914</v>
       </c>
       <c r="I80" t="n">
-        <v>0.01282616578225291</v>
+        <v>0.02956655116141626</v>
       </c>
       <c r="J80" t="n">
         <v>3.734375</v>
       </c>
       <c r="K80" t="n">
-        <v>0.276041666666667</v>
+        <v>0.322916666666667</v>
       </c>
     </row>
     <row r="81">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3899,19 +3899,19 @@
         <v>32</v>
       </c>
       <c r="G81" t="n">
-        <v>2.234375</v>
+        <v>2.401041666666667</v>
       </c>
       <c r="H81" t="n">
-        <v>0.5939651326913445</v>
+        <v>0.4517178977412616</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1049991932786043</v>
+        <v>0.07985319716904438</v>
       </c>
       <c r="J81" t="n">
         <v>1.354166666666667</v>
       </c>
       <c r="K81" t="n">
-        <v>0.8802083333333333</v>
+        <v>1.046875</v>
       </c>
     </row>
     <row r="82">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3942,19 +3942,19 @@
         <v>32</v>
       </c>
       <c r="G82" t="n">
-        <v>3.453125</v>
+        <v>3.526041666666667</v>
       </c>
       <c r="H82" t="n">
-        <v>0.4301253776537629</v>
+        <v>0.3254700901310173</v>
       </c>
       <c r="I82" t="n">
-        <v>0.07603614282485011</v>
+        <v>0.05753552695125978</v>
       </c>
       <c r="J82" t="n">
         <v>2.229166666666667</v>
       </c>
       <c r="K82" t="n">
-        <v>1.223958333333333</v>
+        <v>1.296875</v>
       </c>
     </row>
     <row r="83">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3985,19 +3985,19 @@
         <v>32</v>
       </c>
       <c r="G83" t="n">
-        <v>4.010416666666667</v>
+        <v>4.020833333333334</v>
       </c>
       <c r="H83" t="n">
-        <v>0.07255575041003112</v>
+        <v>0.1015118687553722</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01282616578225291</v>
+        <v>0.01794493269196062</v>
       </c>
       <c r="J83" t="n">
         <v>3.734375</v>
       </c>
       <c r="K83" t="n">
-        <v>0.276041666666667</v>
+        <v>0.2864583333333339</v>
       </c>
     </row>
     <row r="84">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4028,19 +4028,19 @@
         <v>32</v>
       </c>
       <c r="G84" t="n">
-        <v>2.234375</v>
+        <v>2.03125</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5939651326913445</v>
+        <v>0.5461456670209284</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1049991932786043</v>
+        <v>0.09654582616653716</v>
       </c>
       <c r="J84" t="n">
         <v>1.354166666666667</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8802083333333333</v>
+        <v>0.6770833333333333</v>
       </c>
     </row>
     <row r="85">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4071,19 +4071,19 @@
         <v>32</v>
       </c>
       <c r="G85" t="n">
-        <v>3.453125</v>
+        <v>3.5625</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4301253776537629</v>
+        <v>0.3510098079892635</v>
       </c>
       <c r="I85" t="n">
-        <v>0.07603614282485011</v>
+        <v>0.06205035387304904</v>
       </c>
       <c r="J85" t="n">
         <v>2.229166666666667</v>
       </c>
       <c r="K85" t="n">
-        <v>1.223958333333333</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="86">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4888,19 +4888,19 @@
         <v>32</v>
       </c>
       <c r="G104" t="n">
-        <v>2.734375</v>
+        <v>2.9296875</v>
       </c>
       <c r="H104" t="n">
-        <v>0.453203205153373</v>
+        <v>0.6757146008295171</v>
       </c>
       <c r="I104" t="n">
-        <v>0.08011576490485703</v>
+        <v>0.1194505940983281</v>
       </c>
       <c r="J104" t="n">
         <v>2.46875</v>
       </c>
       <c r="K104" t="n">
-        <v>0.265625</v>
+        <v>0.4609375</v>
       </c>
     </row>
     <row r="105">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4931,19 +4931,19 @@
         <v>32</v>
       </c>
       <c r="G105" t="n">
-        <v>1.9609375</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>0.2847563687016131</v>
+        <v>0.290993847623689</v>
       </c>
       <c r="I105" t="n">
-        <v>0.05033828982374185</v>
+        <v>0.05144093073456884</v>
       </c>
       <c r="J105" t="n">
         <v>1.3125</v>
       </c>
       <c r="K105" t="n">
-        <v>0.6484375</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="106">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
         <v>32</v>
       </c>
       <c r="G106" t="n">
-        <v>2.3359375</v>
+        <v>2.1953125</v>
       </c>
       <c r="H106" t="n">
-        <v>0.3735691789369312</v>
+        <v>0.3795921782310505</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0660383249171487</v>
+        <v>0.06710305082813708</v>
       </c>
       <c r="J106" t="n">
         <v>1.7109375</v>
       </c>
       <c r="K106" t="n">
-        <v>0.625</v>
+        <v>0.484375</v>
       </c>
     </row>
     <row r="107">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5017,19 +5017,19 @@
         <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>2.734375</v>
+        <v>2.6875</v>
       </c>
       <c r="H107" t="n">
-        <v>0.453203205153373</v>
+        <v>0.421211769587116</v>
       </c>
       <c r="I107" t="n">
-        <v>0.08011576490485703</v>
+        <v>0.07446042464765881</v>
       </c>
       <c r="J107" t="n">
         <v>2.46875</v>
       </c>
       <c r="K107" t="n">
-        <v>0.265625</v>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="108">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5060,19 +5060,19 @@
         <v>32</v>
       </c>
       <c r="G108" t="n">
-        <v>1.9609375</v>
+        <v>2.0078125</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2847563687016131</v>
+        <v>0.249873960163403</v>
       </c>
       <c r="I108" t="n">
-        <v>0.05033828982374185</v>
+        <v>0.04417189291836988</v>
       </c>
       <c r="J108" t="n">
         <v>1.3125</v>
       </c>
       <c r="K108" t="n">
-        <v>0.6484375</v>
+        <v>0.6953125</v>
       </c>
     </row>
     <row r="109">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5103,19 +5103,19 @@
         <v>32</v>
       </c>
       <c r="G109" t="n">
-        <v>2.3359375</v>
+        <v>2.453125</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3735691789369312</v>
+        <v>0.485422579455428</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0660383249171487</v>
+        <v>0.08581139941849969</v>
       </c>
       <c r="J109" t="n">
         <v>1.7109375</v>
       </c>
       <c r="K109" t="n">
-        <v>0.625</v>
+        <v>0.7421875</v>
       </c>
     </row>
     <row r="110">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5920,19 +5920,19 @@
         <v>32</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9745926816239316</v>
+        <v>0.9889993686868688</v>
       </c>
       <c r="H128" t="n">
-        <v>0.05054638321251809</v>
+        <v>0.03071077218021904</v>
       </c>
       <c r="I128" t="n">
-        <v>0.008935422583506351</v>
+        <v>0.005428948816027014</v>
       </c>
       <c r="J128" t="n">
         <v>0.9450247975064152</v>
       </c>
       <c r="K128" t="n">
-        <v>0.02956788411751643</v>
+        <v>0.04397457118045356</v>
       </c>
     </row>
     <row r="129">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5963,19 +5963,19 @@
         <v>32</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3226982303740721</v>
+        <v>0.4130962011307406</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2318724924584012</v>
+        <v>0.2020150138961032</v>
       </c>
       <c r="I129" t="n">
-        <v>0.04098965294699052</v>
+        <v>0.0357115465568573</v>
       </c>
       <c r="J129" t="n">
         <v>0.1474739774829163</v>
       </c>
       <c r="K129" t="n">
-        <v>0.1752242528911558</v>
+        <v>0.2656222236478243</v>
       </c>
     </row>
     <row r="130">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6006,19 +6006,19 @@
         <v>32</v>
       </c>
       <c r="G130" t="n">
-        <v>0.7352005724538619</v>
+        <v>0.7735815011925209</v>
       </c>
       <c r="H130" t="n">
-        <v>0.101848478778466</v>
+        <v>0.09624511268276728</v>
       </c>
       <c r="I130" t="n">
-        <v>0.01800443749944687</v>
+        <v>0.01701389295851203</v>
       </c>
       <c r="J130" t="n">
         <v>0.4271739153255529</v>
       </c>
       <c r="K130" t="n">
-        <v>0.3080266571283091</v>
+        <v>0.346407585866968</v>
       </c>
     </row>
     <row r="131">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6049,19 +6049,19 @@
         <v>32</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9745926816239316</v>
+        <v>0.9627232142857143</v>
       </c>
       <c r="H131" t="n">
-        <v>0.05054638321251809</v>
+        <v>0.05903906884914606</v>
       </c>
       <c r="I131" t="n">
-        <v>0.008935422583506351</v>
+        <v>0.01043673148454266</v>
       </c>
       <c r="J131" t="n">
         <v>0.9450247975064152</v>
       </c>
       <c r="K131" t="n">
-        <v>0.02956788411751643</v>
+        <v>0.01769841677929906</v>
       </c>
     </row>
     <row r="132">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6092,19 +6092,19 @@
         <v>32</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3226982303740721</v>
+        <v>0.2814641990169273</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2318724924584012</v>
+        <v>0.1846698310379603</v>
       </c>
       <c r="I132" t="n">
-        <v>0.04098965294699052</v>
+        <v>0.03264532245187893</v>
       </c>
       <c r="J132" t="n">
         <v>0.1474739774829163</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1752242528911558</v>
+        <v>0.1339902215340111</v>
       </c>
     </row>
     <row r="133">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6135,19 +6135,19 @@
         <v>32</v>
       </c>
       <c r="G133" t="n">
-        <v>0.7352005724538619</v>
+        <v>0.7596610032876481</v>
       </c>
       <c r="H133" t="n">
-        <v>0.101848478778466</v>
+        <v>0.08549914672634747</v>
       </c>
       <c r="I133" t="n">
-        <v>0.01800443749944687</v>
+        <v>0.01511425660896597</v>
       </c>
       <c r="J133" t="n">
         <v>0.4271739153255529</v>
       </c>
       <c r="K133" t="n">
-        <v>0.3080266571283091</v>
+        <v>0.3324870879620952</v>
       </c>
     </row>
     <row r="134">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -6952,19 +6952,19 @@
         <v>32</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4208680555555556</v>
+        <v>0.5548493693806194</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1684333577261302</v>
+        <v>0.1986178576223017</v>
       </c>
       <c r="I152" t="n">
-        <v>0.02977509235654156</v>
+        <v>0.03511100849736844</v>
       </c>
       <c r="J152" t="n">
         <v>0.2979604076479077</v>
       </c>
       <c r="K152" t="n">
-        <v>0.1229076479076479</v>
+        <v>0.2568889617327117</v>
       </c>
     </row>
     <row r="153">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -6995,19 +6995,19 @@
         <v>32</v>
       </c>
       <c r="G153" t="n">
-        <v>0.6464295017632866</v>
+        <v>0.6500056606190507</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2451604062535511</v>
+        <v>0.1689413350867142</v>
       </c>
       <c r="I153" t="n">
-        <v>0.04333864643508371</v>
+        <v>0.02986489091563111</v>
       </c>
       <c r="J153" t="n">
         <v>0.4127582463331302</v>
       </c>
       <c r="K153" t="n">
-        <v>0.2336712554301564</v>
+        <v>0.2372474142859205</v>
       </c>
     </row>
     <row r="154">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7038,19 +7038,19 @@
         <v>32</v>
       </c>
       <c r="G154" t="n">
-        <v>0.6581695822134895</v>
+        <v>0.6784833829365079</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2345852468674586</v>
+        <v>0.1925502851746766</v>
       </c>
       <c r="I154" t="n">
-        <v>0.04146920470657506</v>
+        <v>0.03403840309160435</v>
       </c>
       <c r="J154" t="n">
         <v>0.2685587671111568</v>
       </c>
       <c r="K154" t="n">
-        <v>0.3896108151023327</v>
+        <v>0.4099246158253511</v>
       </c>
     </row>
     <row r="155">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7081,19 +7081,19 @@
         <v>32</v>
       </c>
       <c r="G155" t="n">
-        <v>0.4208680555555556</v>
+        <v>0.5192549117549117</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1684333577261302</v>
+        <v>0.2374383283662946</v>
       </c>
       <c r="I155" t="n">
-        <v>0.02977509235654156</v>
+        <v>0.04197356302535126</v>
       </c>
       <c r="J155" t="n">
         <v>0.2979604076479077</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1229076479076479</v>
+        <v>0.221294504107004</v>
       </c>
     </row>
     <row r="156">
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7124,19 +7124,19 @@
         <v>32</v>
       </c>
       <c r="G156" t="n">
-        <v>0.6464295017632866</v>
+        <v>0.6080900736494104</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2451604062535511</v>
+        <v>0.206293605146242</v>
       </c>
       <c r="I156" t="n">
-        <v>0.04333864643508371</v>
+        <v>0.03646790177858193</v>
       </c>
       <c r="J156" t="n">
         <v>0.4127582463331302</v>
       </c>
       <c r="K156" t="n">
-        <v>0.2336712554301564</v>
+        <v>0.1953318273162801</v>
       </c>
     </row>
     <row r="157">
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7167,19 +7167,19 @@
         <v>32</v>
       </c>
       <c r="G157" t="n">
-        <v>0.6581695822134895</v>
+        <v>0.6115092355185234</v>
       </c>
       <c r="H157" t="n">
-        <v>0.2345852468674586</v>
+        <v>0.1782200548959014</v>
       </c>
       <c r="I157" t="n">
-        <v>0.04146920470657506</v>
+        <v>0.03150515234008266</v>
       </c>
       <c r="J157" t="n">
         <v>0.2685587671111568</v>
       </c>
       <c r="K157" t="n">
-        <v>0.3896108151023327</v>
+        <v>0.3429504684073666</v>
       </c>
     </row>
     <row r="158">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -7984,19 +7984,19 @@
         <v>32</v>
       </c>
       <c r="G176" t="n">
-        <v>3.65</v>
+        <v>3.36875</v>
       </c>
       <c r="H176" t="n">
-        <v>0.4428645755285294</v>
+        <v>0.8682342110060454</v>
       </c>
       <c r="I176" t="n">
-        <v>0.07828813612588127</v>
+        <v>0.1534835745651316</v>
       </c>
       <c r="J176" t="n">
         <v>2.39375</v>
       </c>
       <c r="K176" t="n">
-        <v>1.256250000000001</v>
+        <v>0.9750000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8027,19 +8027,19 @@
         <v>32</v>
       </c>
       <c r="G177" t="n">
-        <v>1.8875</v>
+        <v>1.94375</v>
       </c>
       <c r="H177" t="n">
-        <v>0.4870914334251107</v>
+        <v>0.4165429923982986</v>
       </c>
       <c r="I177" t="n">
-        <v>0.08610641390819289</v>
+        <v>0.07363509364514337</v>
       </c>
       <c r="J177" t="n">
         <v>1.0625</v>
       </c>
       <c r="K177" t="n">
-        <v>0.825</v>
+        <v>0.8812499999999999</v>
       </c>
     </row>
     <row r="178">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8070,19 +8070,19 @@
         <v>32</v>
       </c>
       <c r="G178" t="n">
-        <v>3.15625</v>
+        <v>2.881250000000001</v>
       </c>
       <c r="H178" t="n">
-        <v>0.4703721930556695</v>
+        <v>0.7091282699383845</v>
       </c>
       <c r="I178" t="n">
-        <v>0.08315084184781293</v>
+        <v>0.1253573521011291</v>
       </c>
       <c r="J178" t="n">
         <v>1.5875</v>
       </c>
       <c r="K178" t="n">
-        <v>1.56875</v>
+        <v>1.293750000000001</v>
       </c>
     </row>
     <row r="179">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8113,19 +8113,19 @@
         <v>32</v>
       </c>
       <c r="G179" t="n">
-        <v>3.65</v>
+        <v>3.49375</v>
       </c>
       <c r="H179" t="n">
-        <v>0.4428645755285294</v>
+        <v>0.5180219823458734</v>
       </c>
       <c r="I179" t="n">
-        <v>0.07828813612588127</v>
+        <v>0.09157421413011627</v>
       </c>
       <c r="J179" t="n">
         <v>2.39375</v>
       </c>
       <c r="K179" t="n">
-        <v>1.256250000000001</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="180">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8156,19 +8156,19 @@
         <v>32</v>
       </c>
       <c r="G180" t="n">
-        <v>1.8875</v>
+        <v>1.75625</v>
       </c>
       <c r="H180" t="n">
-        <v>0.4870914334251107</v>
+        <v>0.4564501880748308</v>
       </c>
       <c r="I180" t="n">
-        <v>0.08610641390819289</v>
+        <v>0.08068975581539696</v>
       </c>
       <c r="J180" t="n">
         <v>1.0625</v>
       </c>
       <c r="K180" t="n">
-        <v>0.825</v>
+        <v>0.6937500000000001</v>
       </c>
     </row>
     <row r="181">
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8199,19 +8199,19 @@
         <v>32</v>
       </c>
       <c r="G181" t="n">
-        <v>3.15625</v>
+        <v>3.35625</v>
       </c>
       <c r="H181" t="n">
-        <v>0.4703721930556695</v>
+        <v>0.5098624102827691</v>
       </c>
       <c r="I181" t="n">
-        <v>0.08315084184781293</v>
+        <v>0.09013179194576593</v>
       </c>
       <c r="J181" t="n">
         <v>1.5875</v>
       </c>
       <c r="K181" t="n">
-        <v>1.56875</v>
+        <v>1.76875</v>
       </c>
     </row>
     <row r="182">
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -9016,19 +9016,19 @@
         <v>32</v>
       </c>
       <c r="G200" t="n">
-        <v>3.362132352941177</v>
+        <v>3.523897058823529</v>
       </c>
       <c r="H200" t="n">
-        <v>0.4480139041481629</v>
+        <v>0.3987813154599845</v>
       </c>
       <c r="I200" t="n">
-        <v>0.07919841742225647</v>
+        <v>0.0704952430930617</v>
       </c>
       <c r="J200" t="n">
         <v>2.626838235294118</v>
       </c>
       <c r="K200" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.8970588235294117</v>
       </c>
     </row>
     <row r="201">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9059,19 +9059,19 @@
         <v>32</v>
       </c>
       <c r="G201" t="n">
-        <v>2.351102941176471</v>
+        <v>2.378676470588236</v>
       </c>
       <c r="H201" t="n">
-        <v>0.2933517066548256</v>
+        <v>0.3334054131986658</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0518577452620685</v>
+        <v>0.05893830713926986</v>
       </c>
       <c r="J201" t="n">
         <v>1.549632352941176</v>
       </c>
       <c r="K201" t="n">
-        <v>0.8014705882352942</v>
+        <v>0.8290441176470591</v>
       </c>
     </row>
     <row r="202">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -9102,19 +9102,19 @@
         <v>32</v>
       </c>
       <c r="G202" t="n">
-        <v>3.012867647058823</v>
+        <v>3.141544117647059</v>
       </c>
       <c r="H202" t="n">
-        <v>0.3855100644892749</v>
+        <v>0.4811108585563036</v>
       </c>
       <c r="I202" t="n">
-        <v>0.06814919520400738</v>
+        <v>0.08504918764691105</v>
       </c>
       <c r="J202" t="n">
         <v>1.786764705882353</v>
       </c>
       <c r="K202" t="n">
-        <v>1.22610294117647</v>
+        <v>1.354779411764706</v>
       </c>
     </row>
     <row r="203">
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -9145,19 +9145,19 @@
         <v>32</v>
       </c>
       <c r="G203" t="n">
-        <v>3.362132352941177</v>
+        <v>3.321691176470588</v>
       </c>
       <c r="H203" t="n">
-        <v>0.4480139041481629</v>
+        <v>0.4524454210448425</v>
       </c>
       <c r="I203" t="n">
-        <v>0.07919841742225647</v>
+        <v>0.07998180633440269</v>
       </c>
       <c r="J203" t="n">
         <v>2.626838235294118</v>
       </c>
       <c r="K203" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.6948529411764706</v>
       </c>
     </row>
     <row r="204">
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -9188,19 +9188,19 @@
         <v>32</v>
       </c>
       <c r="G204" t="n">
-        <v>2.351102941176471</v>
+        <v>2.194852941176471</v>
       </c>
       <c r="H204" t="n">
-        <v>0.2933517066548256</v>
+        <v>0.3213007592920426</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0518577452620685</v>
+        <v>0.05679848642394748</v>
       </c>
       <c r="J204" t="n">
         <v>1.549632352941176</v>
       </c>
       <c r="K204" t="n">
-        <v>0.8014705882352942</v>
+        <v>0.6452205882352942</v>
       </c>
     </row>
     <row r="205">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -9231,19 +9231,19 @@
         <v>32</v>
       </c>
       <c r="G205" t="n">
-        <v>3.012867647058823</v>
+        <v>3.349264705882353</v>
       </c>
       <c r="H205" t="n">
-        <v>0.3855100644892749</v>
+        <v>0.4439665098400809</v>
       </c>
       <c r="I205" t="n">
-        <v>0.06814919520400738</v>
+        <v>0.07848293243191132</v>
       </c>
       <c r="J205" t="n">
         <v>1.786764705882353</v>
       </c>
       <c r="K205" t="n">
-        <v>1.22610294117647</v>
+        <v>1.5625</v>
       </c>
     </row>
     <row r="206">
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -10033,19 +10033,19 @@
         <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.956495098039216</v>
+        <v>2.95796568627451</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6802076019688694</v>
+        <v>0.6523517613680626</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09817951052538915</v>
+        <v>0.09415886625804437</v>
       </c>
       <c r="J6" t="n">
         <v>1.857107843137255</v>
       </c>
       <c r="K6" t="n">
-        <v>1.099387254901961</v>
+        <v>1.100857843137255</v>
       </c>
     </row>
     <row r="7">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -10076,19 +10076,19 @@
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.850122549019608</v>
+        <v>2.787990196078431</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7153577527348811</v>
+        <v>0.7800491722224533</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1032529977770923</v>
+        <v>0.1125903998909445</v>
       </c>
       <c r="J7" t="n">
         <v>1.811887254901961</v>
       </c>
       <c r="K7" t="n">
-        <v>1.038235294117647</v>
+        <v>0.9761029411764703</v>
       </c>
     </row>
     <row r="8">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10119,19 +10119,19 @@
         <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.956495098039216</v>
+        <v>2.934803921568628</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6802076019688694</v>
+        <v>0.8021513014068606</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09817951052538915</v>
+        <v>0.1157805674495149</v>
       </c>
       <c r="J8" t="n">
         <v>1.857107843137255</v>
       </c>
       <c r="K8" t="n">
-        <v>1.099387254901961</v>
+        <v>1.077696078431373</v>
       </c>
     </row>
     <row r="9">
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10162,19 +10162,19 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>2.850122549019608</v>
+        <v>2.88921568627451</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7153577527348811</v>
+        <v>0.7609199952985432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1032529977770923</v>
+        <v>0.1098293410293457</v>
       </c>
       <c r="J9" t="n">
         <v>1.811887254901961</v>
       </c>
       <c r="K9" t="n">
-        <v>1.038235294117647</v>
+        <v>1.077328431372549</v>
       </c>
     </row>
     <row r="10">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -10721,19 +10721,19 @@
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>3.024305555555556</v>
+        <v>2.980902777777777</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9125404122229932</v>
+        <v>0.8385016298460791</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1317138631608393</v>
+        <v>0.1210272854268934</v>
       </c>
       <c r="J22" t="n">
         <v>2.288194444444444</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7361111111111116</v>
+        <v>0.692708333333333</v>
       </c>
     </row>
     <row r="23">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -10764,19 +10764,19 @@
         <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.895833333333333</v>
+        <v>2.934027777777777</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9987433001873058</v>
+        <v>0.8714608149140466</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1441561783036191</v>
+        <v>0.1257845340197089</v>
       </c>
       <c r="J23" t="n">
         <v>2.041666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>0.854166666666667</v>
+        <v>0.8923611111111107</v>
       </c>
     </row>
     <row r="24">
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -10807,19 +10807,19 @@
         <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>3.024305555555556</v>
+        <v>2.909722222222223</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9125404122229932</v>
+        <v>0.9933040200666338</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1317138631608393</v>
+        <v>0.1433710858431521</v>
       </c>
       <c r="J24" t="n">
         <v>2.288194444444444</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7361111111111116</v>
+        <v>0.6215277777777786</v>
       </c>
     </row>
     <row r="25">
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -10850,19 +10850,19 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>2.895833333333333</v>
+        <v>2.866319444444444</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9987433001873058</v>
+        <v>0.9546049247991278</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1441561783036191</v>
+        <v>0.1377853525756297</v>
       </c>
       <c r="J25" t="n">
         <v>2.041666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.854166666666667</v>
+        <v>0.8246527777777777</v>
       </c>
     </row>
     <row r="26">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -11409,19 +11409,19 @@
         <v>48</v>
       </c>
       <c r="G38" t="n">
-        <v>2.966145833333333</v>
+        <v>2.989583333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8386204728177568</v>
+        <v>0.8258753147182648</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1210444389323158</v>
+        <v>0.1192048338174143</v>
       </c>
       <c r="J38" t="n">
         <v>2.197916666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>0.768229166666667</v>
+        <v>0.791666666666667</v>
       </c>
     </row>
     <row r="39">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -11452,19 +11452,19 @@
         <v>48</v>
       </c>
       <c r="G39" t="n">
-        <v>2.783854166666667</v>
+        <v>2.880208333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8811484524763228</v>
+        <v>0.8853710355367267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1271828240583068</v>
+        <v>0.1277923014249567</v>
       </c>
       <c r="J39" t="n">
         <v>1.984375</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7994791666666665</v>
+        <v>0.8958333333333335</v>
       </c>
     </row>
     <row r="40">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -11495,19 +11495,19 @@
         <v>48</v>
       </c>
       <c r="G40" t="n">
-        <v>2.966145833333333</v>
+        <v>2.8828125</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8386204728177568</v>
+        <v>0.8345140682176614</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1210444389323158</v>
+        <v>0.1204517304819991</v>
       </c>
       <c r="J40" t="n">
         <v>2.197916666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>0.768229166666667</v>
+        <v>0.6848958333333335</v>
       </c>
     </row>
     <row r="41">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -11538,19 +11538,19 @@
         <v>48</v>
       </c>
       <c r="G41" t="n">
-        <v>2.783854166666667</v>
+        <v>2.700520833333333</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8811484524763228</v>
+        <v>0.8686087185492191</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1271828240583068</v>
+        <v>0.1253728693687119</v>
       </c>
       <c r="J41" t="n">
         <v>1.984375</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7994791666666665</v>
+        <v>0.7161458333333335</v>
       </c>
     </row>
     <row r="42">
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -12097,19 +12097,19 @@
         <v>48</v>
       </c>
       <c r="G54" t="n">
-        <v>3.28125</v>
+        <v>3.322916666666667</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8093398719751761</v>
+        <v>0.6836543528945592</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1168181482376913</v>
+        <v>0.0986770061690833</v>
       </c>
       <c r="J54" t="n">
         <v>2.524305555555556</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7569444444444442</v>
+        <v>0.7986111111111107</v>
       </c>
     </row>
     <row r="55">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -12140,19 +12140,19 @@
         <v>48</v>
       </c>
       <c r="G55" t="n">
-        <v>3.184027777777777</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9065297556029467</v>
+        <v>0.8539990754115503</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1308462996064417</v>
+        <v>0.1232641490191375</v>
       </c>
       <c r="J55" t="n">
         <v>2.354166666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8298611111111107</v>
+        <v>0.979166666666667</v>
       </c>
     </row>
     <row r="56">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -12183,19 +12183,19 @@
         <v>48</v>
       </c>
       <c r="G56" t="n">
-        <v>3.28125</v>
+        <v>3.21875</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8093398719751761</v>
+        <v>0.9547419601137741</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1168181482376913</v>
+        <v>0.1378051319195796</v>
       </c>
       <c r="J56" t="n">
         <v>2.524305555555556</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7569444444444442</v>
+        <v>0.6944444444444442</v>
       </c>
     </row>
     <row r="57">
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -12226,19 +12226,19 @@
         <v>48</v>
       </c>
       <c r="G57" t="n">
-        <v>3.184027777777777</v>
+        <v>3.190972222222222</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9065297556029467</v>
+        <v>0.9225245346019122</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1308462996064417</v>
+        <v>0.1331549470966121</v>
       </c>
       <c r="J57" t="n">
         <v>2.354166666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8298611111111107</v>
+        <v>0.8368055555555554</v>
       </c>
     </row>
     <row r="58">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -12785,19 +12785,19 @@
         <v>48</v>
       </c>
       <c r="G70" t="n">
-        <v>2.421875</v>
+        <v>2.380208333333333</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4588267009333281</v>
+        <v>0.5530129835085953</v>
       </c>
       <c r="I70" t="n">
-        <v>0.06622592982381123</v>
+        <v>0.07982054872351139</v>
       </c>
       <c r="J70" t="n">
         <v>1.765625</v>
       </c>
       <c r="K70" t="n">
-        <v>0.65625</v>
+        <v>0.6145833333333335</v>
       </c>
     </row>
     <row r="71">
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -12828,19 +12828,19 @@
         <v>48</v>
       </c>
       <c r="G71" t="n">
-        <v>2.265625</v>
+        <v>2.369791666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5115845482420281</v>
+        <v>0.6880236561474029</v>
       </c>
       <c r="I71" t="n">
-        <v>0.07384086916019701</v>
+        <v>0.09930766077138341</v>
       </c>
       <c r="J71" t="n">
         <v>1.895833333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3697916666666667</v>
+        <v>0.4739583333333333</v>
       </c>
     </row>
     <row r="72">
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -12871,19 +12871,19 @@
         <v>48</v>
       </c>
       <c r="G72" t="n">
-        <v>2.421875</v>
+        <v>2.4375</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4588267009333281</v>
+        <v>0.4740612223681573</v>
       </c>
       <c r="I72" t="n">
-        <v>0.06622592982381123</v>
+        <v>0.06842484358665467</v>
       </c>
       <c r="J72" t="n">
         <v>1.765625</v>
       </c>
       <c r="K72" t="n">
-        <v>0.65625</v>
+        <v>0.671875</v>
       </c>
     </row>
     <row r="73">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -12914,19 +12914,19 @@
         <v>48</v>
       </c>
       <c r="G73" t="n">
-        <v>2.265625</v>
+        <v>2.328125</v>
       </c>
       <c r="H73" t="n">
-        <v>0.5115845482420281</v>
+        <v>0.4950721256286482</v>
       </c>
       <c r="I73" t="n">
-        <v>0.07384086916019701</v>
+        <v>0.07145750624999507</v>
       </c>
       <c r="J73" t="n">
         <v>1.895833333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3697916666666667</v>
+        <v>0.4322916666666667</v>
       </c>
     </row>
     <row r="74">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -13473,19 +13473,19 @@
         <v>48</v>
       </c>
       <c r="G86" t="n">
-        <v>0.699088046009002</v>
+        <v>0.7286242144794777</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2949433747004748</v>
+        <v>0.2546123530738583</v>
       </c>
       <c r="I86" t="n">
-        <v>0.04257140919475395</v>
+        <v>0.03675012764654904</v>
       </c>
       <c r="J86" t="n">
         <v>0.5110360802055091</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1880519658034929</v>
+        <v>0.2175881342739686</v>
       </c>
     </row>
     <row r="87">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -13516,19 +13516,19 @@
         <v>48</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6559062769589085</v>
+        <v>0.7218271661939425</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3226687220820985</v>
+        <v>0.2899881338960541</v>
       </c>
       <c r="I87" t="n">
-        <v>0.04657321838829303</v>
+        <v>0.04185618179167102</v>
       </c>
       <c r="J87" t="n">
         <v>0.5020790466710804</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1538272302878281</v>
+        <v>0.2197481195228621</v>
       </c>
     </row>
     <row r="88">
@@ -13548,7 +13548,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -13559,19 +13559,19 @@
         <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>0.699088046009002</v>
+        <v>0.6694907842522975</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2949433747004748</v>
+        <v>0.3167354434366582</v>
       </c>
       <c r="I88" t="n">
-        <v>0.04257140919475395</v>
+        <v>0.04571682338251253</v>
       </c>
       <c r="J88" t="n">
         <v>0.5110360802055091</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1880519658034929</v>
+        <v>0.1584547040467884</v>
       </c>
     </row>
     <row r="89">
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -13602,19 +13602,19 @@
         <v>48</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6559062769589085</v>
+        <v>0.6664081601412289</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3226687220820985</v>
+        <v>0.3096352420157786</v>
       </c>
       <c r="I89" t="n">
-        <v>0.04657321838829303</v>
+        <v>0.04469199758210118</v>
       </c>
       <c r="J89" t="n">
         <v>0.5020790466710804</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1538272302878281</v>
+        <v>0.1643291134701486</v>
       </c>
     </row>
     <row r="90">
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -14161,19 +14161,19 @@
         <v>48</v>
       </c>
       <c r="G102" t="n">
-        <v>0.5633979047877075</v>
+        <v>0.5705994512167113</v>
       </c>
       <c r="H102" t="n">
-        <v>0.2629434033969018</v>
+        <v>0.1865665083852313</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0379526111832094</v>
+        <v>0.02692855595949547</v>
       </c>
       <c r="J102" t="n">
         <v>0.2788127898789663</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2845851149087411</v>
+        <v>0.2917866613377449</v>
       </c>
     </row>
     <row r="103">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -14204,19 +14204,19 @@
         <v>48</v>
       </c>
       <c r="G103" t="n">
-        <v>0.5869135215671804</v>
+        <v>0.6849594907407409</v>
       </c>
       <c r="H103" t="n">
-        <v>0.2226832406825554</v>
+        <v>0.1830887452231773</v>
       </c>
       <c r="I103" t="n">
-        <v>0.03214155723802289</v>
+        <v>0.02642658408504806</v>
       </c>
       <c r="J103" t="n">
         <v>0.3740388241824968</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2128746973846836</v>
+        <v>0.3109206665582441</v>
       </c>
     </row>
     <row r="104">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -14247,19 +14247,19 @@
         <v>48</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5633979047877075</v>
+        <v>0.571192520213418</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2629434033969018</v>
+        <v>0.2259544950213558</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0379526111832094</v>
+        <v>0.03261372213129643</v>
       </c>
       <c r="J104" t="n">
         <v>0.2788127898789663</v>
       </c>
       <c r="K104" t="n">
-        <v>0.2845851149087411</v>
+        <v>0.2923797303344517</v>
       </c>
     </row>
     <row r="105">
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -14290,19 +14290,19 @@
         <v>48</v>
       </c>
       <c r="G105" t="n">
-        <v>0.5869135215671804</v>
+        <v>0.5880436270684789</v>
       </c>
       <c r="H105" t="n">
-        <v>0.2226832406825554</v>
+        <v>0.1967963168994569</v>
       </c>
       <c r="I105" t="n">
-        <v>0.03214155723802289</v>
+        <v>0.02840510163435709</v>
       </c>
       <c r="J105" t="n">
         <v>0.3740388241824968</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2128746973846836</v>
+        <v>0.2140048028859821</v>
       </c>
     </row>
     <row r="106">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -14849,19 +14849,19 @@
         <v>48</v>
       </c>
       <c r="G118" t="n">
-        <v>2.979166666666667</v>
+        <v>2.858333333333333</v>
       </c>
       <c r="H118" t="n">
-        <v>0.8212492646023672</v>
+        <v>0.8594489410485672</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1185371209974897</v>
+        <v>0.1240507693672823</v>
       </c>
       <c r="J118" t="n">
         <v>1.7375</v>
       </c>
       <c r="K118" t="n">
-        <v>1.241666666666666</v>
+        <v>1.120833333333333</v>
       </c>
     </row>
     <row r="119">
@@ -14881,7 +14881,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -14892,19 +14892,19 @@
         <v>48</v>
       </c>
       <c r="G119" t="n">
-        <v>2.816666666666666</v>
+        <v>2.604166666666667</v>
       </c>
       <c r="H119" t="n">
-        <v>0.9324717401075976</v>
+        <v>0.9412437071832441</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1345907025407101</v>
+        <v>0.1358568269288218</v>
       </c>
       <c r="J119" t="n">
         <v>1.625</v>
       </c>
       <c r="K119" t="n">
-        <v>1.191666666666666</v>
+        <v>0.9791666666666665</v>
       </c>
     </row>
     <row r="120">
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -14935,19 +14935,19 @@
         <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>2.979166666666667</v>
+        <v>2.9125</v>
       </c>
       <c r="H120" t="n">
-        <v>0.8212492646023672</v>
+        <v>0.9960827531203569</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1185371209974897</v>
+        <v>0.1437721614122954</v>
       </c>
       <c r="J120" t="n">
         <v>1.7375</v>
       </c>
       <c r="K120" t="n">
-        <v>1.241666666666666</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="121">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -14978,19 +14978,19 @@
         <v>48</v>
       </c>
       <c r="G121" t="n">
-        <v>2.816666666666666</v>
+        <v>2.825000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>0.9324717401075976</v>
+        <v>0.8719018098142971</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1345907025407101</v>
+        <v>0.1258481861508016</v>
       </c>
       <c r="J121" t="n">
         <v>1.625</v>
       </c>
       <c r="K121" t="n">
-        <v>1.191666666666666</v>
+        <v>1.200000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -15537,19 +15537,19 @@
         <v>48</v>
       </c>
       <c r="G134" t="n">
-        <v>2.933823529411764</v>
+        <v>3.057598039215686</v>
       </c>
       <c r="H134" t="n">
-        <v>0.5886888114065495</v>
+        <v>0.5559989988711195</v>
       </c>
       <c r="I134" t="n">
-        <v>0.08496991093362305</v>
+        <v>0.08025154291685083</v>
       </c>
       <c r="J134" t="n">
         <v>1.97671568627451</v>
       </c>
       <c r="K134" t="n">
-        <v>0.9571078431372546</v>
+        <v>1.080882352941176</v>
       </c>
     </row>
     <row r="135">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -15580,19 +15580,19 @@
         <v>48</v>
       </c>
       <c r="G135" t="n">
-        <v>2.88357843137255</v>
+        <v>2.971813725490196</v>
       </c>
       <c r="H135" t="n">
-        <v>0.5462473402365473</v>
+        <v>0.6934649976119596</v>
       </c>
       <c r="I135" t="n">
-        <v>0.07884401223242192</v>
+        <v>0.100093050761212</v>
       </c>
       <c r="J135" t="n">
         <v>1.998774509803922</v>
       </c>
       <c r="K135" t="n">
-        <v>0.8848039215686281</v>
+        <v>0.9730392156862748</v>
       </c>
     </row>
     <row r="136">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -15623,19 +15623,19 @@
         <v>48</v>
       </c>
       <c r="G136" t="n">
-        <v>2.933823529411764</v>
+        <v>2.957107843137255</v>
       </c>
       <c r="H136" t="n">
-        <v>0.5886888114065495</v>
+        <v>0.6647086051461435</v>
       </c>
       <c r="I136" t="n">
-        <v>0.08496991093362305</v>
+        <v>0.09594242302844666</v>
       </c>
       <c r="J136" t="n">
         <v>1.97671568627451</v>
       </c>
       <c r="K136" t="n">
-        <v>0.9571078431372546</v>
+        <v>0.9803921568627449</v>
       </c>
     </row>
     <row r="137">
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -15666,19 +15666,19 @@
         <v>48</v>
       </c>
       <c r="G137" t="n">
-        <v>2.88357843137255</v>
+        <v>2.953431372549019</v>
       </c>
       <c r="H137" t="n">
-        <v>0.5462473402365473</v>
+        <v>0.6943104814058704</v>
       </c>
       <c r="I137" t="n">
-        <v>0.07884401223242192</v>
+        <v>0.1002150858352145</v>
       </c>
       <c r="J137" t="n">
         <v>1.998774509803922</v>
       </c>
       <c r="K137" t="n">
-        <v>0.8848039215686281</v>
+        <v>0.9546568627450978</v>
       </c>
     </row>
     <row r="138">
